--- a/BOM/lora_bom.xlsx
+++ b/BOM/lora_bom.xlsx
@@ -1028,7 +1028,7 @@
         <v>36</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0.12</v>
